--- a/portfolio-lab/dist/examples/portfolio-example.xlsx
+++ b/portfolio-lab/dist/examples/portfolio-example.xlsx
@@ -415,7 +415,7 @@
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" customWidth="1"/>
   </cols>
@@ -449,7 +449,7 @@
         <v>ОФЗ / RGBITR</v>
       </c>
       <c r="J1" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="K1" t="str">
         <v>Серебро</v>
@@ -487,7 +487,7 @@
         <v>100</v>
       </c>
       <c r="J2" s="1">
-        <v>4200</v>
+        <v>100</v>
       </c>
       <c r="K2" s="1">
         <v>38</v>
@@ -525,7 +525,7 @@
         <v>101.621877</v>
       </c>
       <c r="J3" s="1">
-        <v>3905.266475</v>
+        <v>99.750754</v>
       </c>
       <c r="K3" s="1">
         <v>34.576805</v>
@@ -563,7 +563,7 @@
         <v>103.38628</v>
       </c>
       <c r="J4" s="1">
-        <v>3649.019986</v>
+        <v>99.775006</v>
       </c>
       <c r="K4" s="1">
         <v>36.051628</v>
@@ -601,7 +601,7 @@
         <v>103.422128</v>
       </c>
       <c r="J5" s="1">
-        <v>3431.358688</v>
+        <v>99.65702</v>
       </c>
       <c r="K5" s="1">
         <v>36.29958</v>
@@ -639,7 +639,7 @@
         <v>104.466507</v>
       </c>
       <c r="J6" s="1">
-        <v>3148.048542</v>
+        <v>99.349422</v>
       </c>
       <c r="K6" s="1">
         <v>35.792777</v>
@@ -677,7 +677,7 @@
         <v>104.176069</v>
       </c>
       <c r="J7" s="1">
-        <v>3174.955829</v>
+        <v>100.327728</v>
       </c>
       <c r="K7" s="1">
         <v>35.518781</v>
@@ -715,7 +715,7 @@
         <v>105.212973</v>
       </c>
       <c r="J8" s="1">
-        <v>3212.254358</v>
+        <v>101.558676</v>
       </c>
       <c r="K8" s="1">
         <v>34.985288</v>
@@ -753,7 +753,7 @@
         <v>105.092828</v>
       </c>
       <c r="J9" s="1">
-        <v>3149.693248</v>
+        <v>102.112732</v>
       </c>
       <c r="K9" s="1">
         <v>34.332704</v>
@@ -791,7 +791,7 @@
         <v>106.541741</v>
       </c>
       <c r="J10" s="1">
-        <v>3272.051119</v>
+        <v>103.51935</v>
       </c>
       <c r="K10" s="1">
         <v>33.040467</v>
@@ -829,7 +829,7 @@
         <v>105.832328</v>
       </c>
       <c r="J11" s="1">
-        <v>3544.227837</v>
+        <v>105.284586</v>
       </c>
       <c r="K11" s="1">
         <v>31.208063</v>
@@ -867,7 +867,7 @@
         <v>107.028101</v>
       </c>
       <c r="J12" s="1">
-        <v>3607.425949</v>
+        <v>106.25056</v>
       </c>
       <c r="K12" s="1">
         <v>30.076234</v>
@@ -905,7 +905,7 @@
         <v>106.879229</v>
       </c>
       <c r="J13" s="1">
-        <v>3856.175501</v>
+        <v>108.169033</v>
       </c>
       <c r="K13" s="1">
         <v>30.41242</v>
@@ -943,7 +943,7 @@
         <v>107.023315</v>
       </c>
       <c r="J14" s="1">
-        <v>3991.212836</v>
+        <v>109.766368</v>
       </c>
       <c r="K14" s="1">
         <v>30.416646</v>
@@ -981,7 +981,7 @@
         <v>106.766614</v>
       </c>
       <c r="J15" s="1">
-        <v>4571.543032</v>
+        <v>112.769281</v>
       </c>
       <c r="K15" s="1">
         <v>32.533267</v>
@@ -1019,7 +1019,7 @@
         <v>107.672422</v>
       </c>
       <c r="J16" s="1">
-        <v>4503.418892</v>
+        <v>113.282935</v>
       </c>
       <c r="K16" s="1">
         <v>29.98103</v>
@@ -1057,7 +1057,7 @@
         <v>108.171243</v>
       </c>
       <c r="J17" s="1">
-        <v>4271.368982</v>
+        <v>113.095104</v>
       </c>
       <c r="K17" s="1">
         <v>31.178776</v>
@@ -1095,7 +1095,7 @@
         <v>109.394452</v>
       </c>
       <c r="J18" s="1">
-        <v>4295.882528</v>
+        <v>113.761999</v>
       </c>
       <c r="K18" s="1">
         <v>30.755832</v>
@@ -1133,7 +1133,7 @@
         <v>111.272812</v>
       </c>
       <c r="J19" s="1">
-        <v>4281.561283</v>
+        <v>114.317111</v>
       </c>
       <c r="K19" s="1">
         <v>28.980138</v>
@@ -1171,7 +1171,7 @@
         <v>110.480789</v>
       </c>
       <c r="J20" s="1">
-        <v>4453.534869</v>
+        <v>115.613878</v>
       </c>
       <c r="K20" s="1">
         <v>27.422859</v>
@@ -1209,7 +1209,7 @@
         <v>110.063279</v>
       </c>
       <c r="J21" s="1">
-        <v>4663.438721</v>
+        <v>116.906938</v>
       </c>
       <c r="K21" s="1">
         <v>27.426975</v>
@@ -1247,7 +1247,7 @@
         <v>110.958277</v>
       </c>
       <c r="J22" s="1">
-        <v>5360.728924</v>
+        <v>119.979193</v>
       </c>
       <c r="K22" s="1">
         <v>27.211275</v>
@@ -1285,7 +1285,7 @@
         <v>110.728082</v>
       </c>
       <c r="J23" s="1">
-        <v>5747.049703</v>
+        <v>121.842519</v>
       </c>
       <c r="K23" s="1">
         <v>30.976606</v>
@@ -1323,7 +1323,7 @@
         <v>110.282985</v>
       </c>
       <c r="J24" s="1">
-        <v>5787.631624</v>
+        <v>122.90035</v>
       </c>
       <c r="K24" s="1">
         <v>32.986116</v>
@@ -1361,7 +1361,7 @@
         <v>110.78757</v>
       </c>
       <c r="J25" s="1">
-        <v>5854.14306</v>
+        <v>123.968143</v>
       </c>
       <c r="K25" s="1">
         <v>33.099892</v>
@@ -1399,7 +1399,7 @@
         <v>111.675272</v>
       </c>
       <c r="J26" s="1">
-        <v>5700.411859</v>
+        <v>124.521201</v>
       </c>
       <c r="K26" s="1">
         <v>31.37473</v>
@@ -1437,7 +1437,7 @@
         <v>112.755201</v>
       </c>
       <c r="J27" s="1">
-        <v>5698.32625</v>
+        <v>125.448101</v>
       </c>
       <c r="K27" s="1">
         <v>30.31422</v>
@@ -1475,7 +1475,7 @@
         <v>113.951749</v>
       </c>
       <c r="J28" s="1">
-        <v>5898.445078</v>
+        <v>126.966073</v>
       </c>
       <c r="K28" s="1">
         <v>29.855274</v>
@@ -1513,7 +1513,7 @@
         <v>114.751012</v>
       </c>
       <c r="J29" s="1">
-        <v>5688.66525</v>
+        <v>127.045546</v>
       </c>
       <c r="K29" s="1">
         <v>31.397979</v>
@@ -1551,7 +1551,7 @@
         <v>114.979465</v>
       </c>
       <c r="J30" s="1">
-        <v>5988.370205</v>
+        <v>128.740502</v>
       </c>
       <c r="K30" s="1">
         <v>32.447715</v>
@@ -1589,7 +1589,7 @@
         <v>116.566336</v>
       </c>
       <c r="J31" s="1">
-        <v>6177.642081</v>
+        <v>130.375832</v>
       </c>
       <c r="K31" s="1">
         <v>31.361</v>
@@ -1627,7 +1627,7 @@
         <v>118.022626</v>
       </c>
       <c r="J32" s="1">
-        <v>6294.787615</v>
+        <v>131.815846</v>
       </c>
       <c r="K32" s="1">
         <v>30.473257</v>
@@ -1665,7 +1665,7 @@
         <v>119.189931</v>
       </c>
       <c r="J33" s="1">
-        <v>5415.233062</v>
+        <v>130.473917</v>
       </c>
       <c r="K33" s="1">
         <v>29.744971</v>
@@ -1703,7 +1703,7 @@
         <v>119.841058</v>
       </c>
       <c r="J34" s="1">
-        <v>5133.493369</v>
+        <v>130.537402</v>
       </c>
       <c r="K34" s="1">
         <v>29.460922</v>
@@ -1741,7 +1741,7 @@
         <v>121.305495</v>
       </c>
       <c r="J35" s="1">
-        <v>4914.955725</v>
+        <v>130.623548</v>
       </c>
       <c r="K35" s="1">
         <v>30.967765</v>
@@ -1779,7 +1779,7 @@
         <v>123.717412</v>
       </c>
       <c r="J36" s="1">
-        <v>4364.07428</v>
+        <v>129.910477</v>
       </c>
       <c r="K36" s="1">
         <v>32.216914</v>
@@ -1817,7 +1817,7 @@
         <v>124.899291</v>
       </c>
       <c r="J37" s="1">
-        <v>4086.822923</v>
+        <v>129.951733</v>
       </c>
       <c r="K37" s="1">
         <v>29.977196</v>
@@ -1855,7 +1855,7 @@
         <v>124.063311</v>
       </c>
       <c r="J38" s="1">
-        <v>4100.140578</v>
+        <v>131.069261</v>
       </c>
       <c r="K38" s="1">
         <v>28.858401</v>
@@ -1893,7 +1893,7 @@
         <v>124.194262</v>
       </c>
       <c r="J39" s="1">
-        <v>4086.939949</v>
+        <v>131.973202</v>
       </c>
       <c r="K39" s="1">
         <v>28.506828</v>
@@ -1931,7 +1931,7 @@
         <v>123.939682</v>
       </c>
       <c r="J40" s="1">
-        <v>4145.31654</v>
+        <v>129.930754</v>
       </c>
       <c r="K40" s="1">
         <v>32.400471</v>
@@ -1969,7 +1969,7 @@
         <v>126.448077</v>
       </c>
       <c r="J41" s="1">
-        <v>3733.166871</v>
+        <v>130.997427</v>
       </c>
       <c r="K41" s="1">
         <v>31.168875</v>
@@ -2007,7 +2007,7 @@
         <v>126.420299</v>
       </c>
       <c r="J42" s="1">
-        <v>3617.579707</v>
+        <v>131.805968</v>
       </c>
       <c r="K42" s="1">
         <v>33.169371</v>
@@ -2045,7 +2045,7 @@
         <v>127.366064</v>
       </c>
       <c r="J43" s="1">
-        <v>3483.922913</v>
+        <v>132.223477</v>
       </c>
       <c r="K43" s="1">
         <v>34.960346</v>
@@ -2083,7 +2083,7 @@
         <v>129.404238</v>
       </c>
       <c r="J44" s="1">
-        <v>3142.869892</v>
+        <v>131.936124</v>
       </c>
       <c r="K44" s="1">
         <v>34.17815</v>
@@ -2121,7 +2121,7 @@
         <v>132.671287</v>
       </c>
       <c r="J45" s="1">
-        <v>3128.773088</v>
+        <v>132.889595</v>
       </c>
       <c r="K45" s="1">
         <v>34.337493</v>
@@ -2159,7 +2159,7 @@
         <v>137.38584</v>
       </c>
       <c r="J46" s="1">
-        <v>2929.41853</v>
+        <v>132.911945</v>
       </c>
       <c r="K46" s="1">
         <v>34.654283</v>
@@ -2197,7 +2197,7 @@
         <v>142.446626</v>
       </c>
       <c r="J47" s="1">
-        <v>2598.180602</v>
+        <v>131.817985</v>
       </c>
       <c r="K47" s="1">
         <v>31.649109</v>
@@ -2235,7 +2235,7 @@
         <v>143.266228</v>
       </c>
       <c r="J48" s="1">
-        <v>2705.11923</v>
+        <v>133.595632</v>
       </c>
       <c r="K48" s="1">
         <v>32.691233</v>
@@ -2273,7 +2273,7 @@
         <v>144.417877</v>
       </c>
       <c r="J49" s="1">
-        <v>2793.872632</v>
+        <v>135.161565</v>
       </c>
       <c r="K49" s="1">
         <v>32.093952</v>
@@ -2311,7 +2311,7 @@
         <v>144.769243</v>
       </c>
       <c r="J50" s="1">
-        <v>2732.364039</v>
+        <v>135.963769</v>
       </c>
       <c r="K50" s="1">
         <v>31.346734</v>
@@ -2349,7 +2349,7 @@
         <v>147.20188</v>
       </c>
       <c r="J51" s="1">
-        <v>2911.193913</v>
+        <v>138.470113</v>
       </c>
       <c r="K51" s="1">
         <v>29.685033</v>
@@ -2387,7 +2387,7 @@
         <v>149.468347</v>
       </c>
       <c r="J52" s="1">
-        <v>2925.845754</v>
+        <v>140.900436</v>
       </c>
       <c r="K52" s="1">
         <v>28.12172</v>
@@ -2425,7 +2425,7 @@
         <v>149.61607</v>
       </c>
       <c r="J53" s="1">
-        <v>2932.556692</v>
+        <v>141.825614</v>
       </c>
       <c r="K53" s="1">
         <v>27.990893</v>
@@ -2463,7 +2463,7 @@
         <v>149.612745</v>
       </c>
       <c r="J54" s="1">
-        <v>2685.453079</v>
+        <v>141.231285</v>
       </c>
       <c r="K54" s="1">
         <v>29.298305</v>
@@ -2501,7 +2501,7 @@
         <v>151.264791</v>
       </c>
       <c r="J55" s="1">
-        <v>2714.561697</v>
+        <v>142.265993</v>
       </c>
       <c r="K55" s="1">
         <v>28.591428</v>
@@ -2539,7 +2539,7 @@
         <v>151.835799</v>
       </c>
       <c r="J56" s="1">
-        <v>2690.139363</v>
+        <v>143.255731</v>
       </c>
       <c r="K56" s="1">
         <v>28.909205</v>
@@ -2577,7 +2577,7 @@
         <v>152.166782</v>
       </c>
       <c r="J57" s="1">
-        <v>2672.730594</v>
+        <v>143.910742</v>
       </c>
       <c r="K57" s="1">
         <v>28.369827</v>
@@ -2615,7 +2615,7 @@
         <v>152.292757</v>
       </c>
       <c r="J58" s="1">
-        <v>2558.766922</v>
+        <v>143.846028</v>
       </c>
       <c r="K58" s="1">
         <v>31.132575</v>
@@ -2653,7 +2653,7 @@
         <v>152.225388</v>
       </c>
       <c r="J59" s="1">
-        <v>2549.257014</v>
+        <v>144.665456</v>
       </c>
       <c r="K59" s="1">
         <v>33.114318</v>
@@ -2691,7 +2691,7 @@
         <v>152.03578</v>
       </c>
       <c r="J60" s="1">
-        <v>2454.362845</v>
+        <v>145.064376</v>
       </c>
       <c r="K60" s="1">
         <v>33.802959</v>
@@ -2729,7 +2729,7 @@
         <v>153.150275</v>
       </c>
       <c r="J61" s="1">
-        <v>2459.85154</v>
+        <v>146.173838</v>
       </c>
       <c r="K61" s="1">
         <v>33.414595</v>
@@ -2767,7 +2767,7 @@
         <v>157.418628</v>
       </c>
       <c r="J62" s="1">
-        <v>2426.590229</v>
+        <v>147.041144</v>
       </c>
       <c r="K62" s="1">
         <v>31.505278</v>
@@ -2805,7 +2805,7 @@
         <v>157.647482</v>
       </c>
       <c r="J63" s="1">
-        <v>2250.618574</v>
+        <v>146.936068</v>
       </c>
       <c r="K63" s="1">
         <v>31.496452</v>
@@ -2843,7 +2843,7 @@
         <v>156.19291</v>
       </c>
       <c r="J64" s="1">
-        <v>2148.703538</v>
+        <v>147.115592</v>
       </c>
       <c r="K64" s="1">
         <v>31.430625</v>
@@ -2881,7 +2881,7 @@
         <v>155.211329</v>
       </c>
       <c r="J65" s="1">
-        <v>2098.041519</v>
+        <v>147.431734</v>
       </c>
       <c r="K65" s="1">
         <v>32.69254</v>
@@ -2919,7 +2919,7 @@
         <v>154.353691</v>
       </c>
       <c r="J66" s="1">
-        <v>1939.772344</v>
+        <v>147.264378</v>
       </c>
       <c r="K66" s="1">
         <v>33.108109</v>
@@ -2957,7 +2957,7 @@
         <v>155.775575</v>
       </c>
       <c r="J67" s="1">
-        <v>1891.20306</v>
+        <v>147.833702</v>
       </c>
       <c r="K67" s="1">
         <v>35.928054</v>
@@ -2995,7 +2995,7 @@
         <v>156.465827</v>
       </c>
       <c r="J68" s="1">
-        <v>1931.839949</v>
+        <v>149.507296</v>
       </c>
       <c r="K68" s="1">
         <v>37.512474</v>
@@ -3033,7 +3033,7 @@
         <v>155.977417</v>
       </c>
       <c r="J69" s="1">
-        <v>2184.730743</v>
+        <v>152.873506</v>
       </c>
       <c r="K69" s="1">
         <v>38.39554</v>
@@ -3071,7 +3071,7 @@
         <v>156.150631</v>
       </c>
       <c r="J70" s="1">
-        <v>1994.857274</v>
+        <v>152.419259</v>
       </c>
       <c r="K70" s="1">
         <v>38.434328</v>
@@ -3109,7 +3109,7 @@
         <v>159.304616</v>
       </c>
       <c r="J71" s="1">
-        <v>2006.185477</v>
+        <v>153.506794</v>
       </c>
       <c r="K71" s="1">
         <v>37.611162</v>
@@ -3147,7 +3147,7 @@
         <v>161.164417</v>
       </c>
       <c r="J72" s="1">
-        <v>1891.478162</v>
+        <v>153.258057</v>
       </c>
       <c r="K72" s="1">
         <v>42.532694</v>
@@ -3185,7 +3185,7 @@
         <v>162.450958</v>
       </c>
       <c r="J73" s="1">
-        <v>1752.29647</v>
+        <v>152.953766</v>
       </c>
       <c r="K73" s="1">
         <v>40.258204</v>
@@ -3223,7 +3223,7 @@
         <v>163.021879</v>
       </c>
       <c r="J74" s="1">
-        <v>1890.821166</v>
+        <v>155.734476</v>
       </c>
       <c r="K74" s="1">
         <v>40.807151</v>
@@ -3261,7 +3261,7 @@
         <v>164.686961</v>
       </c>
       <c r="J75" s="1">
-        <v>2011.069776</v>
+        <v>158.032378</v>
       </c>
       <c r="K75" s="1">
         <v>42.702334</v>
@@ -3299,7 +3299,7 @@
         <v>164.876576</v>
       </c>
       <c r="J76" s="1">
-        <v>2158.77098</v>
+        <v>160.468237</v>
       </c>
       <c r="K76" s="1">
         <v>40.955386</v>
@@ -3337,7 +3337,7 @@
         <v>168.601727</v>
       </c>
       <c r="J77" s="1">
-        <v>2149.523501</v>
+        <v>161.712711</v>
       </c>
       <c r="K77" s="1">
         <v>40.442162</v>
@@ -3375,7 +3375,7 @@
         <v>170.534124</v>
       </c>
       <c r="J78" s="1">
-        <v>2050.989486</v>
+        <v>161.534353</v>
       </c>
       <c r="K78" s="1">
         <v>44.250199</v>
@@ -3413,7 +3413,7 @@
         <v>170.98297</v>
       </c>
       <c r="J79" s="1">
-        <v>1983.319294</v>
+        <v>162.141518</v>
       </c>
       <c r="K79" s="1">
         <v>47.446538</v>
@@ -3451,7 +3451,7 @@
         <v>173.037423</v>
       </c>
       <c r="J80" s="1">
-        <v>1902.474888</v>
+        <v>162.609412</v>
       </c>
       <c r="K80" s="1">
         <v>44.140851</v>
@@ -3489,7 +3489,7 @@
         <v>173.157897</v>
       </c>
       <c r="J81" s="1">
-        <v>1652.662646</v>
+        <v>161.249912</v>
       </c>
       <c r="K81" s="1">
         <v>42.151516</v>
@@ -3527,7 +3527,7 @@
         <v>171.08838</v>
       </c>
       <c r="J82" s="1">
-        <v>1597.665532</v>
+        <v>161.922</v>
       </c>
       <c r="K82" s="1">
         <v>43.801366</v>
@@ -3565,7 +3565,7 @@
         <v>171.096788</v>
       </c>
       <c r="J83" s="1">
-        <v>1562.352184</v>
+        <v>162.682411</v>
       </c>
       <c r="K83" s="1">
         <v>43.190208</v>
@@ -3603,7 +3603,7 @@
         <v>173.611395</v>
       </c>
       <c r="J84" s="1">
-        <v>1518.922534</v>
+        <v>163.320054</v>
       </c>
       <c r="K84" s="1">
         <v>45.054008</v>
@@ -3641,7 +3641,7 @@
         <v>176.972118</v>
       </c>
       <c r="J85" s="1">
-        <v>1518.362658</v>
+        <v>164.393281</v>
       </c>
       <c r="K85" s="1">
         <v>47.193693</v>
@@ -3679,7 +3679,7 @@
         <v>177.626695</v>
       </c>
       <c r="J86" s="1">
-        <v>1366.641408</v>
+        <v>163.565079</v>
       </c>
       <c r="K86" s="1">
         <v>44.947979</v>
@@ -4007,16 +4007,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="C9" t="str">
-        <v>₽ за баррель; учебный уровень</v>
+        <v>Индекс рублёвых цен на жильё, январь 2019 = 100</v>
       </c>
       <c r="D9" t="str">
         <v>Синтетический ряд demoData()</v>
       </c>
       <c r="E9" t="str">
-        <v>Не котировки Brent.</v>
+        <v>Учебная динамика стоимости жилья, без арендного дохода; не реальные цены недвижимости.</v>
       </c>
     </row>
     <row r="10">
